--- a/outputs/figure_source_data/source_data_fig_5_d.xlsx
+++ b/outputs/figure_source_data/source_data_fig_5_d.xlsx
@@ -1977,7 +1977,7 @@
         <v>631.0799999999865</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>972.3000000000052</v>
+        <v>972.3000000000048</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>0.435</v>
